--- a/data/processed/puma_sentiment.xlsx
+++ b/data/processed/puma_sentiment.xlsx
@@ -434,12 +434,12 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Leadership_context_human</t>
+          <t>Leadership_context</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Information_valence_human</t>
+          <t>Information_valence</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">

--- a/data/processed/puma_sentiment.xlsx
+++ b/data/processed/puma_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z106"/>
+  <dimension ref="A1:AB106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,6 +547,16 @@
           <t>finbert_n_chunks</t>
         </is>
       </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>financial_roberta_score</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>finbert_score</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -653,6 +663,12 @@
       <c r="Z2" t="n">
         <v>1</v>
       </c>
+      <c r="AA2" t="n">
+        <v>0.0003248054417781532</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-0.3427483178675175</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -755,6 +771,12 @@
       <c r="Z3" t="n">
         <v>1</v>
       </c>
+      <c r="AA3" t="n">
+        <v>-0.9982335649401648</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-0.3866129219532013</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -857,6 +879,12 @@
       <c r="Z4" t="n">
         <v>1</v>
       </c>
+      <c r="AA4" t="n">
+        <v>0.9974757675663568</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9289869554340839</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -959,6 +987,12 @@
       <c r="Z5" t="n">
         <v>1</v>
       </c>
+      <c r="AA5" t="n">
+        <v>0.08212288841605186</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-0.2275363206863403</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1061,6 +1095,12 @@
       <c r="Z6" t="n">
         <v>1</v>
       </c>
+      <c r="AA6" t="n">
+        <v>-0.998740122988238</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-0.9432848328724504</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1163,6 +1203,12 @@
       <c r="Z7" t="n">
         <v>1</v>
       </c>
+      <c r="AA7" t="n">
+        <v>0.9937087298894767</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.5343839498236775</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1265,6 +1311,12 @@
       <c r="Z8" t="n">
         <v>1</v>
       </c>
+      <c r="AA8" t="n">
+        <v>0.9974703417101409</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.2469153106212616</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1367,6 +1419,12 @@
       <c r="Z9" t="n">
         <v>1</v>
       </c>
+      <c r="AA9" t="n">
+        <v>0.9960614215524402</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8156098816543818</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1469,6 +1527,12 @@
       <c r="Z10" t="n">
         <v>1</v>
       </c>
+      <c r="AA10" t="n">
+        <v>0.001232205991982482</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.3848900683224201</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1571,6 +1635,12 @@
       <c r="Z11" t="n">
         <v>1</v>
       </c>
+      <c r="AA11" t="n">
+        <v>0.9957121306506451</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-0.687338151037693</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1681,6 +1751,12 @@
       <c r="Z12" t="n">
         <v>1</v>
       </c>
+      <c r="AA12" t="n">
+        <v>0.9938964502362069</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.4074841216206551</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1783,6 +1859,12 @@
       <c r="Z13" t="n">
         <v>1</v>
       </c>
+      <c r="AA13" t="n">
+        <v>0.9975959258736111</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8490793853998184</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1889,6 +1971,12 @@
       <c r="Z14" t="n">
         <v>1</v>
       </c>
+      <c r="AA14" t="n">
+        <v>0.9208393546578009</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8683460494503379</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1991,6 +2079,12 @@
       <c r="Z15" t="n">
         <v>1</v>
       </c>
+      <c r="AA15" t="n">
+        <v>0.9974961609113961</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.1968884933739901</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2093,6 +2187,12 @@
       <c r="Z16" t="n">
         <v>1</v>
       </c>
+      <c r="AA16" t="n">
+        <v>0.9965594318928197</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9381561335176229</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2203,6 +2303,12 @@
       <c r="Z17" t="n">
         <v>1</v>
       </c>
+      <c r="AA17" t="n">
+        <v>0.9968596037942916</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.6746411267668009</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2305,6 +2411,12 @@
       <c r="Z18" t="n">
         <v>1</v>
       </c>
+      <c r="AA18" t="n">
+        <v>-0.9978145950008184</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-0.2870492339134216</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2407,6 +2519,12 @@
       <c r="Z19" t="n">
         <v>1</v>
       </c>
+      <c r="AA19" t="n">
+        <v>0.01303241345158312</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.5414681937545538</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2515,6 +2633,12 @@
       <c r="Z20" t="n">
         <v>1</v>
       </c>
+      <c r="AA20" t="n">
+        <v>0.01117673463886604</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.7525706067681313</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2621,6 +2745,12 @@
       <c r="Z21" t="n">
         <v>1</v>
       </c>
+      <c r="AA21" t="n">
+        <v>0.0003248054417781532</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-0.3427483178675175</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2723,6 +2853,12 @@
       <c r="Z22" t="n">
         <v>1</v>
       </c>
+      <c r="AA22" t="n">
+        <v>-0.9986785151122604</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>-0.9233857560902834</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2825,6 +2961,12 @@
       <c r="Z23" t="n">
         <v>1</v>
       </c>
+      <c r="AA23" t="n">
+        <v>0.9974830772844143</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0.6048976257443428</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2927,6 +3069,12 @@
       <c r="Z24" t="n">
         <v>1</v>
       </c>
+      <c r="AA24" t="n">
+        <v>-0.9986400279158261</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>-0.9012885186821222</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3029,6 +3177,12 @@
       <c r="Z25" t="n">
         <v>1</v>
       </c>
+      <c r="AA25" t="n">
+        <v>0.9973428188823164</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0.9337506666779518</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3131,6 +3285,12 @@
       <c r="Z26" t="n">
         <v>1</v>
       </c>
+      <c r="AA26" t="n">
+        <v>0.9970680501719471</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.6472060112282634</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3233,6 +3393,12 @@
       <c r="Z27" t="n">
         <v>1</v>
       </c>
+      <c r="AA27" t="n">
+        <v>0.9963568490347825</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.7558590043336153</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3343,6 +3509,12 @@
       <c r="Z28" t="n">
         <v>1</v>
       </c>
+      <c r="AA28" t="n">
+        <v>-0.9971281306934543</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>-0.9372059507295489</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3445,6 +3617,12 @@
       <c r="Z29" t="n">
         <v>1</v>
       </c>
+      <c r="AA29" t="n">
+        <v>-0.9987484220182523</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>-0.7646705582737923</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3547,6 +3725,12 @@
       <c r="Z30" t="n">
         <v>1</v>
       </c>
+      <c r="AA30" t="n">
+        <v>0.9970289863995276</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0.8951973365619779</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3649,6 +3833,12 @@
       <c r="Z31" t="n">
         <v>1</v>
       </c>
+      <c r="AA31" t="n">
+        <v>0.9967619579983875</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.4704696061089635</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3752,6 +3942,12 @@
       <c r="Z32" t="n">
         <v>1</v>
       </c>
+      <c r="AA32" t="n">
+        <v>0.997536652314011</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.8449777234345675</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3858,6 +4054,12 @@
       <c r="Z33" t="n">
         <v>1</v>
       </c>
+      <c r="AA33" t="n">
+        <v>0.9973623332916759</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0.7277763551101089</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3960,6 +4162,12 @@
       <c r="Z34" t="n">
         <v>1</v>
       </c>
+      <c r="AA34" t="n">
+        <v>0.9976462902850471</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.9140595560893416</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4061,6 +4269,12 @@
       </c>
       <c r="Z35" t="n">
         <v>1</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.9930817057320382</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.9057074561715126</v>
       </c>
     </row>
     <row r="36">
@@ -4171,6 +4385,12 @@
       <c r="Z36" t="n">
         <v>1</v>
       </c>
+      <c r="AA36" t="n">
+        <v>0.05003743463021237</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0.3815098665654659</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4277,6 +4497,12 @@
       <c r="Z37" t="n">
         <v>1</v>
       </c>
+      <c r="AA37" t="n">
+        <v>0.0003248054417781532</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>-0.3427483178675175</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4379,6 +4605,12 @@
       <c r="Z38" t="n">
         <v>1</v>
       </c>
+      <c r="AA38" t="n">
+        <v>0.001281961136555765</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0.2461190419271588</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4481,6 +4713,12 @@
       <c r="Z39" t="n">
         <v>1</v>
       </c>
+      <c r="AA39" t="n">
+        <v>0.9973207857692614</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0.9380413657054305</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4583,6 +4821,12 @@
       <c r="Z40" t="n">
         <v>1</v>
       </c>
+      <c r="AA40" t="n">
+        <v>0.994864357431652</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0.8277983879670501</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4685,6 +4929,12 @@
       <c r="Z41" t="n">
         <v>1</v>
       </c>
+      <c r="AA41" t="n">
+        <v>0.9952100943628466</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0.8363754539750516</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4787,6 +5037,12 @@
       <c r="Z42" t="n">
         <v>1</v>
       </c>
+      <c r="AA42" t="n">
+        <v>0.9976542167714797</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0.887295838445425</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4889,6 +5145,12 @@
       <c r="Z43" t="n">
         <v>1</v>
       </c>
+      <c r="AA43" t="n">
+        <v>0.9976173060713336</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0.9330724589526653</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4991,6 +5253,12 @@
       <c r="Z44" t="n">
         <v>1</v>
       </c>
+      <c r="AA44" t="n">
+        <v>0.9975726727279834</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0.8078317940235138</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5093,6 +5361,12 @@
       <c r="Z45" t="n">
         <v>1</v>
       </c>
+      <c r="AA45" t="n">
+        <v>0.9975375689682551</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0.8717134185135365</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5195,6 +5469,12 @@
       <c r="Z46" t="n">
         <v>1</v>
       </c>
+      <c r="AA46" t="n">
+        <v>0.9976144276151899</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0.720228074118495</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5305,6 +5585,12 @@
       <c r="Z47" t="n">
         <v>1</v>
       </c>
+      <c r="AA47" t="n">
+        <v>0.9975880705169402</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0.910074251703918</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5407,6 +5693,12 @@
       <c r="Z48" t="n">
         <v>1</v>
       </c>
+      <c r="AA48" t="n">
+        <v>0.972901317072683</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0.5693141557276249</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5509,6 +5801,12 @@
       <c r="Z49" t="n">
         <v>1</v>
       </c>
+      <c r="AA49" t="n">
+        <v>0.9850589525303803</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>0.2912054499611259</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5611,6 +5909,12 @@
       <c r="Z50" t="n">
         <v>1</v>
       </c>
+      <c r="AA50" t="n">
+        <v>0.9975989063386805</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0.8065143558196723</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5713,6 +6017,12 @@
       <c r="Z51" t="n">
         <v>1</v>
       </c>
+      <c r="AA51" t="n">
+        <v>0.9976165452389978</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>0.7071379078552127</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5815,6 +6125,12 @@
       <c r="Z52" t="n">
         <v>1</v>
       </c>
+      <c r="AA52" t="n">
+        <v>0.06549925729632378</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>0.9330850038677454</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5917,6 +6233,12 @@
       <c r="Z53" t="n">
         <v>1</v>
       </c>
+      <c r="AA53" t="n">
+        <v>0.9977607598411851</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>0.842174204532057</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6019,6 +6341,12 @@
       <c r="Z54" t="n">
         <v>1</v>
       </c>
+      <c r="AA54" t="n">
+        <v>0.0002208284422522411</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0.8135813735425472</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6121,6 +6449,12 @@
       <c r="Z55" t="n">
         <v>1</v>
       </c>
+      <c r="AA55" t="n">
+        <v>0.9978056088439189</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>0.8961538672447205</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6228,6 +6562,12 @@
       <c r="Z56" t="n">
         <v>1</v>
       </c>
+      <c r="AA56" t="n">
+        <v>4.593181074596941e-05</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>0.01258345879614353</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6334,6 +6674,12 @@
       <c r="Z57" t="n">
         <v>1</v>
       </c>
+      <c r="AA57" t="n">
+        <v>0.0003248054417781532</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>-0.3427483178675175</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6436,6 +6782,12 @@
       <c r="Z58" t="n">
         <v>1</v>
       </c>
+      <c r="AA58" t="n">
+        <v>0.9487734278663993</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>0.9184249676764011</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6538,6 +6890,12 @@
       <c r="Z59" t="n">
         <v>1</v>
       </c>
+      <c r="AA59" t="n">
+        <v>0.996461567847291</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>0.6595968464389443</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6645,6 +7003,12 @@
       <c r="Z60" t="n">
         <v>1</v>
       </c>
+      <c r="AA60" t="n">
+        <v>0.3864150857552886</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>0.8500881567597389</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6751,6 +7115,12 @@
       <c r="Z61" t="n">
         <v>1</v>
       </c>
+      <c r="AA61" t="n">
+        <v>0.9974185272294562</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>0.712197182700038</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6853,6 +7223,12 @@
       <c r="Z62" t="n">
         <v>1</v>
       </c>
+      <c r="AA62" t="n">
+        <v>0.9974806631216779</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>0.7245613895356655</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6955,6 +7331,12 @@
       <c r="Z63" t="n">
         <v>1</v>
       </c>
+      <c r="AA63" t="n">
+        <v>-0.9979493499849923</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>0.8267295192927122</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -7057,6 +7439,12 @@
       <c r="Z64" t="n">
         <v>1</v>
       </c>
+      <c r="AA64" t="n">
+        <v>0.9976195853378158</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>0.6276652198284864</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7159,6 +7547,12 @@
       <c r="Z65" t="n">
         <v>1</v>
       </c>
+      <c r="AA65" t="n">
+        <v>0.0207254944689339</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>0.7134929932653904</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7261,6 +7655,12 @@
       <c r="Z66" t="n">
         <v>1</v>
       </c>
+      <c r="AA66" t="n">
+        <v>0.9975082835590001</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>0.9295184342190623</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7363,6 +7763,12 @@
       <c r="Z67" t="n">
         <v>1</v>
       </c>
+      <c r="AA67" t="n">
+        <v>-0.9684256581240334</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>0.9105253033339977</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7465,6 +7871,12 @@
       <c r="Z68" t="n">
         <v>1</v>
       </c>
+      <c r="AA68" t="n">
+        <v>0.9976594887848478</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>0.6726617757230997</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7567,6 +7979,12 @@
       <c r="Z69" t="n">
         <v>1</v>
       </c>
+      <c r="AA69" t="n">
+        <v>0.9976227025035769</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>0.8784663709811866</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7669,6 +8087,12 @@
       <c r="Z70" t="n">
         <v>1</v>
       </c>
+      <c r="AA70" t="n">
+        <v>0.99757463298738</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>0.6886686319485307</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7771,6 +8195,12 @@
       <c r="Z71" t="n">
         <v>1</v>
       </c>
+      <c r="AA71" t="n">
+        <v>0.07832095437333919</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>0.4507927596569061</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -7873,6 +8303,12 @@
       <c r="Z72" t="n">
         <v>1</v>
       </c>
+      <c r="AA72" t="n">
+        <v>0.9976377885323018</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>0.9228421030566096</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -7975,6 +8411,12 @@
       <c r="Z73" t="n">
         <v>1</v>
       </c>
+      <c r="AA73" t="n">
+        <v>0.9921270081977127</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>0.8966359598562121</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -8077,6 +8519,12 @@
       <c r="Z74" t="n">
         <v>1</v>
       </c>
+      <c r="AA74" t="n">
+        <v>0.997694289078936</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>0.9103680858388543</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -8179,6 +8627,12 @@
       <c r="Z75" t="n">
         <v>1</v>
       </c>
+      <c r="AA75" t="n">
+        <v>0.9974716672440991</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.7251884751021862</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -8281,6 +8735,12 @@
       <c r="Z76" t="n">
         <v>1</v>
       </c>
+      <c r="AA76" t="n">
+        <v>0.7539556318661198</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>0.2268037479370832</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -8383,6 +8843,12 @@
       <c r="Z77" t="n">
         <v>1</v>
       </c>
+      <c r="AA77" t="n">
+        <v>0.000924699183087796</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>0.7575023518875241</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -8485,6 +8951,12 @@
       <c r="Z78" t="n">
         <v>1</v>
       </c>
+      <c r="AA78" t="n">
+        <v>0.9977119357790798</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>0.8720558639615774</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -8592,6 +9064,12 @@
       <c r="Z79" t="n">
         <v>1</v>
       </c>
+      <c r="AA79" t="n">
+        <v>-5.352302105166018e-05</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>0.009581258520483971</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -8698,6 +9176,12 @@
       <c r="Z80" t="n">
         <v>1</v>
       </c>
+      <c r="AA80" t="n">
+        <v>0.0003248054417781532</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>-0.3427483178675175</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -8800,6 +9284,12 @@
       <c r="Z81" t="n">
         <v>1</v>
       </c>
+      <c r="AA81" t="n">
+        <v>0.9972451768699102</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>0.9462616592645645</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -8902,6 +9392,12 @@
       <c r="Z82" t="n">
         <v>1</v>
       </c>
+      <c r="AA82" t="n">
+        <v>-0.9967940889473539</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>-0.9175977725535631</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -9008,6 +9504,12 @@
       <c r="Z83" t="n">
         <v>1</v>
       </c>
+      <c r="AA83" t="n">
+        <v>0.9977700291201472</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>0.863856662530452</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -9110,6 +9612,12 @@
       <c r="Z84" t="n">
         <v>1</v>
       </c>
+      <c r="AA84" t="n">
+        <v>0.9976506748353131</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>0.8333600028418005</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -9212,6 +9720,12 @@
       <c r="Z85" t="n">
         <v>1</v>
       </c>
+      <c r="AA85" t="n">
+        <v>0.9975625204388052</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>0.9246385348960757</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -9314,6 +9828,12 @@
       <c r="Z86" t="n">
         <v>1</v>
       </c>
+      <c r="AA86" t="n">
+        <v>0.9976365503389388</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>0.8474951218813658</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -9416,6 +9936,12 @@
       <c r="Z87" t="n">
         <v>1</v>
       </c>
+      <c r="AA87" t="n">
+        <v>0.9974836703040637</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>0.9075856087729335</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -9518,6 +10044,12 @@
       <c r="Z88" t="n">
         <v>1</v>
       </c>
+      <c r="AA88" t="n">
+        <v>-0.9208034500479698</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>0.9116311930119991</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -9620,6 +10152,12 @@
       <c r="Z89" t="n">
         <v>1</v>
       </c>
+      <c r="AA89" t="n">
+        <v>1.980896922759712e-05</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>0.7588151674717665</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -9727,6 +10265,12 @@
       <c r="Z90" t="n">
         <v>1</v>
       </c>
+      <c r="AA90" t="n">
+        <v>-5.352302105166018e-05</v>
+      </c>
+      <c r="AB90" t="n">
+        <v>0.009581258520483971</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -9833,6 +10377,12 @@
       <c r="Z91" t="n">
         <v>1</v>
       </c>
+      <c r="AA91" t="n">
+        <v>0.0003248054417781532</v>
+      </c>
+      <c r="AB91" t="n">
+        <v>-0.3427483178675175</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -9935,6 +10485,12 @@
       <c r="Z92" t="n">
         <v>1</v>
       </c>
+      <c r="AA92" t="n">
+        <v>0.0008677475270815194</v>
+      </c>
+      <c r="AB92" t="n">
+        <v>0.2121516792103648</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -10037,6 +10593,12 @@
       <c r="Z93" t="n">
         <v>1</v>
       </c>
+      <c r="AA93" t="n">
+        <v>0.9969651702558622</v>
+      </c>
+      <c r="AB93" t="n">
+        <v>0.4735265299677849</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -10139,6 +10701,12 @@
       <c r="Z94" t="n">
         <v>1</v>
       </c>
+      <c r="AA94" t="n">
+        <v>0.9956175691040698</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>0.3577495794743299</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -10241,6 +10809,12 @@
       <c r="Z95" t="n">
         <v>1</v>
       </c>
+      <c r="AA95" t="n">
+        <v>0.9974326933152042</v>
+      </c>
+      <c r="AB95" t="n">
+        <v>0.662287212908268</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -10343,6 +10917,12 @@
       <c r="Z96" t="n">
         <v>1</v>
       </c>
+      <c r="AA96" t="n">
+        <v>0.9951139757176861</v>
+      </c>
+      <c r="AB96" t="n">
+        <v>0.8787451377138495</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -10445,6 +11025,12 @@
       <c r="Z97" t="n">
         <v>1</v>
       </c>
+      <c r="AA97" t="n">
+        <v>-0.9985371263755951</v>
+      </c>
+      <c r="AB97" t="n">
+        <v>-0.9586931122466922</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -10547,6 +11133,12 @@
       <c r="Z98" t="n">
         <v>1</v>
       </c>
+      <c r="AA98" t="n">
+        <v>0.9975555945420638</v>
+      </c>
+      <c r="AB98" t="n">
+        <v>0.8397216079756618</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -10649,6 +11241,12 @@
       <c r="Z99" t="n">
         <v>1</v>
       </c>
+      <c r="AA99" t="n">
+        <v>0.0009534605778753757</v>
+      </c>
+      <c r="AB99" t="n">
+        <v>0.7923717498779297</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -10755,6 +11353,12 @@
       <c r="Z100" t="n">
         <v>1</v>
       </c>
+      <c r="AA100" t="n">
+        <v>0.9965123106376268</v>
+      </c>
+      <c r="AB100" t="n">
+        <v>0.8590172659605742</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -10857,6 +11461,12 @@
       <c r="Z101" t="n">
         <v>1</v>
       </c>
+      <c r="AA101" t="n">
+        <v>0.9977273317635991</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>0.5042427591979504</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -10959,6 +11569,12 @@
       <c r="Z102" t="n">
         <v>1</v>
       </c>
+      <c r="AA102" t="n">
+        <v>0.9966077196295373</v>
+      </c>
+      <c r="AB102" t="n">
+        <v>-0.9325774759054184</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -11061,6 +11677,12 @@
       <c r="Z103" t="n">
         <v>1</v>
       </c>
+      <c r="AA103" t="n">
+        <v>0.9975579243618995</v>
+      </c>
+      <c r="AB103" t="n">
+        <v>0.9071110226213932</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -11163,6 +11785,12 @@
       <c r="Z104" t="n">
         <v>1</v>
       </c>
+      <c r="AA104" t="n">
+        <v>3.628384729381651e-05</v>
+      </c>
+      <c r="AB104" t="n">
+        <v>0.7017231844365597</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -11265,6 +11893,12 @@
       <c r="Z105" t="n">
         <v>1</v>
       </c>
+      <c r="AA105" t="n">
+        <v>6.735704664606601e-05</v>
+      </c>
+      <c r="AB105" t="n">
+        <v>0.7540893256664276</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -11371,6 +12005,12 @@
       </c>
       <c r="Z106" t="n">
         <v>1</v>
+      </c>
+      <c r="AA106" t="n">
+        <v>6.288272561505437e-05</v>
+      </c>
+      <c r="AB106" t="n">
+        <v>0.0107142087072134</v>
       </c>
     </row>
   </sheetData>
